--- a/data/trans_dic/IP28_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura</t>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,81</t>
+          <t>0,6; 5,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,57</t>
+          <t>0,42; 5,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,2</t>
+          <t>0,52; 5,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 3,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,35</t>
+          <t>0,22; 2,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,2</t>
+          <t>1,03; 4,15</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,37</t>
+          <t>0,27; 2,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,37</t>
+          <t>0,44; 3,18</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,88</t>
+          <t>0,66; 3,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,79</t>
+          <t>0,31; 2,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,51</t>
+          <t>0,57; 3,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,8</t>
+          <t>0,67; 3,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,83</t>
+          <t>0,32; 2,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,78</t>
+          <t>0,29; 2,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,8</t>
+          <t>0,83; 2,97</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,21</t>
+          <t>0,49; 2,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,94</t>
+          <t>0,33; 2,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,46</t>
+          <t>0,16; 1,49</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,15</t>
+          <t>0,42; 4,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,21</t>
+          <t>0,71; 5,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,53</t>
+          <t>0,49; 4,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,35</t>
+          <t>0,4; 3,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,59</t>
+          <t>0,26; 3,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,84</t>
+          <t>0,48; 2,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,5</t>
+          <t>0,42; 2,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,36</t>
+          <t>0,39; 2,37</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 3,55</t>
+          <t>0,79; 3,42</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,01</t>
+          <t>0,38; 3,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,84</t>
+          <t>1,91; 6,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,45</t>
+          <t>0,38; 3,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,56</t>
+          <t>0,47; 4,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,23</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,74</t>
+          <t>0,65; 3,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,32</t>
+          <t>0,43; 2,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,57</t>
+          <t>1,62; 4,38</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,42</t>
+          <t>0,38; 2,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,58</t>
+          <t>0,46; 2,81</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,17</t>
+          <t>0,72; 2,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,03</t>
+          <t>1,16; 3,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,81</t>
+          <t>0,5; 1,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,56</t>
+          <t>0,78; 2,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,65; 1,99</t>
+          <t>0,66; 2,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,63</t>
+          <t>0,99; 2,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,73</t>
+          <t>0,49; 1,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,78</t>
+          <t>0,49; 1,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,81</t>
+          <t>0,83; 1,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,59</t>
+          <t>1,33; 2,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,55</t>
+          <t>0,62; 1,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 1,78</t>
+          <t>0,77; 1,78</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2821</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2388</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2681</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5924</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2128</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>3697</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4113</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>758; 7168</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2803</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>490; 6625</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5232</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>738; 7684</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5072</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5369</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>645; 5950</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2755; 11070</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>687; 6369</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1127; 8165</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3258</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1807</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>6551</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>4516</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3748</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2429</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1282; 7092</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3765</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>569; 4322</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1185; 7149</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1362; 7881</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>622; 5843</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>742; 6761</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3327; 11922</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1891; 8871</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1271; 7990</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>690; 6595</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1053</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1094</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4360</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3785</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>3157</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3073</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>6677</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3571</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>593; 5789</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3844</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1342; 10214</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>725; 7325</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4288</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>627; 5336</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>471; 6857</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1375; 7844</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1224; 6856</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1160; 7080</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2951; 12805</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3276</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7596</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2784</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2794</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4626</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>10875</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4085</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4191</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>782; 7897</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3741; 12790</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>695; 7120</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>790; 7440</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4762</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1255; 7162</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3990</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5086</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1761; 10257</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>6280; 17009</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1402; 8943</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1584; 9779</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>8832</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>13052</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6372</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>9542</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>7453</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>17642</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>24471</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>13033</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>16995</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>4849; 15464</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7527; 20054</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3196; 11478</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5190; 17119</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4692; 14804</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6807; 17821</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3251; 11437</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>3703; 13771</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>11499; 25294</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>17707; 33627</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>8073; 19699</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>10908; 25233</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP28_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,72</t>
+          <t>0,59; 5,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,68</t>
+          <t>0,43; 5,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,43</t>
+          <t>0,51; 5,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,82</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,06</t>
+          <t>0,26; 2,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,15</t>
+          <t>1,05; 4,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,54</t>
+          <t>0,27; 2,23</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,18</t>
+          <t>0,41; 3,19</t>
         </is>
       </c>
     </row>
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,67</t>
+          <t>0,67; 3,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,33</t>
+          <t>0,31; 2,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,43</t>
+          <t>0,63; 3,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,87</t>
+          <t>0,65; 4,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,98</t>
+          <t>0,32; 2,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,67</t>
+          <t>0,28; 2,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,97</t>
+          <t>0,81; 2,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,3</t>
+          <t>0,5; 2,22</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,09</t>
+          <t>0,33; 1,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,49</t>
+          <t>0,16; 1,46</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,06</t>
+          <t>0,41; 3,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 5,39</t>
+          <t>0,72; 5,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,91</t>
+          <t>0,44; 4,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,43</t>
+          <t>0,4; 3,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 3,72</t>
+          <t>0,27; 3,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,75</t>
+          <t>0,48; 2,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,33</t>
+          <t>0,41; 2,42</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,37</t>
+          <t>0,39; 2,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,42</t>
+          <t>0,77; 3,4</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,85</t>
+          <t>0,38; 3,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,53</t>
+          <t>1,93; 6,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,86</t>
+          <t>0,38; 3,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,46</t>
+          <t>0,49; 4,81</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,72</t>
+          <t>0,65; 3,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,49</t>
+          <t>0,43; 2,34</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,38</t>
+          <t>1,73; 4,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,42</t>
+          <t>0,38; 2,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,81</t>
+          <t>0,48; 2,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,31</t>
+          <t>0,73; 2,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,1</t>
+          <t>1,28; 3,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,5; 1,81</t>
+          <t>0,51; 1,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,58</t>
+          <t>0,76; 2,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,07</t>
+          <t>0,68; 2,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,59</t>
+          <t>1,01; 2,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,71</t>
+          <t>0,49; 1,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,82</t>
+          <t>0,49; 1,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 1,82</t>
+          <t>0,86; 1,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,52</t>
+          <t>1,28; 2,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,51</t>
+          <t>0,63; 1,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,78</t>
+          <t>0,74; 1,83</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
+          <t>Menores cuyo peso es bastante mayor de lo normal en relación con su altura (tasa de respuesta: 94,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4113</t>
+          <t>0; 4372</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>758; 7168</t>
+          <t>737; 6761</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2803</t>
+          <t>0; 3470</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>490; 6625</t>
+          <t>503; 6963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5232</t>
+          <t>0; 5159</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>738; 7684</t>
+          <t>723; 7410</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5072</t>
+          <t>0; 5333</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5369</t>
+          <t>0; 4325</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>645; 5950</t>
+          <t>764; 6978</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2755; 11070</t>
+          <t>2812; 11629</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>687; 6369</t>
+          <t>679; 5594</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1127; 8165</t>
+          <t>1063; 8188</t>
         </is>
       </c>
     </row>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1282; 7092</t>
+          <t>1291; 7152</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3765</t>
+          <t>0; 3720</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>569; 4322</t>
+          <t>572; 4881</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1873,42 +1873,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1185; 7149</t>
+          <t>1304; 7044</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1362; 7881</t>
+          <t>1330; 8348</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>622; 5843</t>
+          <t>622; 5185</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>742; 6761</t>
+          <t>706; 6704</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3327; 11922</t>
+          <t>3265; 11313</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1891; 8871</t>
+          <t>1930; 8581</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1271; 7990</t>
+          <t>1266; 7489</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>690; 6595</t>
+          <t>694; 6446</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3571</t>
+          <t>0; 3844</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>593; 5789</t>
+          <t>589; 5514</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3844</t>
+          <t>0; 3617</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1342; 10214</t>
+          <t>1362; 9600</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>725; 7325</t>
+          <t>653; 6723</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4288</t>
+          <t>0; 3634</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>627; 5336</t>
+          <t>622; 5400</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>471; 6857</t>
+          <t>489; 6993</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1375; 7844</t>
+          <t>1357; 7436</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1224; 6856</t>
+          <t>1194; 7121</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1160; 7080</t>
+          <t>1150; 6777</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2951; 12805</t>
+          <t>2888; 12701</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>782; 7897</t>
+          <t>779; 8032</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3741; 12790</t>
+          <t>3783; 13441</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>695; 7120</t>
+          <t>701; 6848</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>790; 7440</t>
+          <t>825; 8016</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4762</t>
+          <t>0; 4731</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1255; 7162</t>
+          <t>1256; 7289</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3990</t>
+          <t>0; 4534</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 5086</t>
+          <t>0; 4324</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1761; 10257</t>
+          <t>1767; 9647</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6280; 17009</t>
+          <t>6699; 17712</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1402; 8943</t>
+          <t>1403; 8869</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1584; 9779</t>
+          <t>1679; 9801</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4849; 15464</t>
+          <t>4925; 14519</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7527; 20054</t>
+          <t>8273; 19521</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3196; 11478</t>
+          <t>3221; 11189</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5190; 17119</t>
+          <t>5014; 16868</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4692; 14804</t>
+          <t>4886; 14795</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6807; 17821</t>
+          <t>6996; 18066</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3251; 11437</t>
+          <t>3262; 11672</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3703; 13771</t>
+          <t>3723; 13517</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11499; 25294</t>
+          <t>11918; 25424</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17707; 33627</t>
+          <t>17071; 33683</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8073; 19699</t>
+          <t>8150; 20111</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10908; 25233</t>
+          <t>10463; 25992</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP28_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP28_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,49 +649,49 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,25%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>2,22%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,39</t>
+          <t>0,53; 5,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 5,97</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,23</t>
+          <t>0,57; 5,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,11</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,38; 5,83</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,42</t>
+          <t>0,22; 2,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,36</t>
+          <t>1,04; 4,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,23</t>
+          <t>0,27; 2,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,19</t>
+          <t>0,45; 3,58</t>
         </is>
       </c>
     </row>
@@ -789,44 +789,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,7</t>
+          <t>0,57; 3,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,66; 3,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,63</t>
+          <t>0,32; 2,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0,26; 2,93</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,67; 3,88</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,68</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,31; 2,79</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,63; 3,38</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,65; 4,1</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,32; 2,64</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 2,65</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,82</t>
+          <t>0,82; 2,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,22</t>
+          <t>0,49; 2,21</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,96</t>
+          <t>0,33; 1,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,46</t>
+          <t>0,15; 1,49</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,77%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,3%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,83</t>
+          <t>0,48; 4,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,87</t>
+          <t>0,0; 2,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,4; 3,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,06</t>
+          <t>0,26; 4,17</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,51</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,42; 4,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,47</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 3,79</t>
+          <t>1,18; 6,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,61</t>
+          <t>0,47; 2,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,42</t>
+          <t>0,41; 2,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,27</t>
+          <t>0,4; 2,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,4</t>
+          <t>0,96; 3,96</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,92</t>
+          <t>0,0; 2,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,86</t>
+          <t>0,65; 3,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,72</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,81</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,48; 4,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,79</t>
+          <t>1,97; 6,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,38; 3,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,49; 4,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,34</t>
+          <t>0,38; 2,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,56</t>
+          <t>1,7; 4,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,4</t>
+          <t>0,37; 2,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,82</t>
+          <t>0,43; 2,72</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,02%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,01%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,17</t>
+          <t>0,65; 1,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,02</t>
+          <t>0,97; 2,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,77</t>
+          <t>0,58; 1,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,55</t>
+          <t>0,52; 1,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,07</t>
+          <t>0,69; 2,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,62</t>
+          <t>1,16; 3,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,75</t>
+          <t>0,49; 1,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,78</t>
+          <t>0,84; 2,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,83</t>
+          <t>0,83; 1,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,52</t>
+          <t>1,34; 2,59</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,55</t>
+          <t>0,62; 1,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,83</t>
+          <t>0,82; 2,01</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1519,32 +1519,32 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1436</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1441</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1245</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2821</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2388</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1441</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>2510</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3767</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4372</t>
+          <t>0; 4809</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>737; 6761</t>
+          <t>747; 7359</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3470</t>
+          <t>0; 5037</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>503; 6963</t>
+          <t>0; 4304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5159</t>
+          <t>0; 3845</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>723; 7410</t>
+          <t>719; 7289</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5333</t>
+          <t>0; 3526</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 4325</t>
+          <t>454; 7016</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>764; 6978</t>
+          <t>638; 6772</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2812; 11629</t>
+          <t>2788; 11209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>679; 5594</t>
+          <t>686; 5944</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1063; 8188</t>
+          <t>1108; 8805</t>
         </is>
       </c>
     </row>
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,44 +1785,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1941</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>3258</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>665</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1807</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1941</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2429</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>6551</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>2354</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1291; 7152</t>
+          <t>1190; 7299</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3720</t>
+          <t>1343; 7741</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>572; 4881</t>
+          <t>623; 5556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>615; 6889</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1295; 7503</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3073</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>571; 5179</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1304; 7044</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1330; 8348</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>622; 5185</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>706; 6704</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3265; 11313</t>
+          <t>3281; 11239</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1930; 8581</t>
+          <t>1899; 8538</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1266; 7489</t>
+          <t>1261; 7392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>694; 6446</t>
+          <t>610; 6247</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2289</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>1053</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1969</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1094</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4360</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1187</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6677</t>
+          <t>6843</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3844</t>
+          <t>718; 6753</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>589; 5514</t>
+          <t>0; 3594</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3617</t>
+          <t>624; 5221</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1362; 9600</t>
+          <t>438; 6988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>653; 6723</t>
+          <t>0; 4150</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3634</t>
+          <t>597; 5920</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>622; 5400</t>
+          <t>0; 4408</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>489; 6993</t>
+          <t>1845; 10626</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1357; 7436</t>
+          <t>1342; 8078</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1194; 7121</t>
+          <t>1196; 7349</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1150; 6777</t>
+          <t>1189; 7041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2888; 12701</t>
+          <t>3092; 12806</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1350</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3278</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1132</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3276</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7596</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2784</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2794</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3278</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1301</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1397</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>4303</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>779; 8032</t>
+          <t>0; 4598</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3783; 13441</t>
+          <t>1242; 7205</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>701; 6848</t>
+          <t>0; 4535</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>825; 8016</t>
+          <t>0; 3886</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4731</t>
+          <t>988; 8211</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1256; 7289</t>
+          <t>3866; 13401</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4534</t>
+          <t>708; 6368</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 4324</t>
+          <t>810; 8087</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1767; 9647</t>
+          <t>1558; 9535</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6699; 17712</t>
+          <t>6604; 17740</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1403; 8869</t>
+          <t>1386; 8968</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1679; 9801</t>
+          <t>1439; 9100</t>
         </is>
       </c>
     </row>
@@ -2346,37 +2346,37 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>12</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>11419</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>6661</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>8832</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>13052</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>6372</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>9542</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>6661</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7453</t>
+          <t>10234</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16995</t>
+          <t>17268</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4925; 14519</t>
+          <t>4679; 14251</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8273; 19521</t>
+          <t>6709; 18126</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3221; 11189</t>
+          <t>3878; 11530</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5014; 16868</t>
+          <t>3633; 12623</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4886; 14795</t>
+          <t>4603; 14566</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6996; 18066</t>
+          <t>7493; 19592</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3262; 11672</t>
+          <t>3113; 11453</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3723; 13517</t>
+          <t>5245; 17750</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11918; 25424</t>
+          <t>11480; 25050</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17071; 33683</t>
+          <t>17910; 34532</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8150; 20111</t>
+          <t>8009; 20213</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10463; 25992</t>
+          <t>10858; 26537</t>
         </is>
       </c>
     </row>
